--- a/AAII_Financials/Quarterly/TANH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TANH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="92">
   <si>
     <t>TANH</t>
   </si>
@@ -803,11 +803,11 @@
       <c r="G8" s="3">
         <v>10300</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>24</v>
+      <c r="H8" s="3">
+        <v>10700</v>
+      </c>
+      <c r="I8" s="3">
+        <v>10700</v>
       </c>
       <c r="J8" s="3">
         <v>10700</v>
@@ -892,11 +892,11 @@
       <c r="G9" s="3">
         <v>8100</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>24</v>
+      <c r="H9" s="3">
+        <v>8600</v>
+      </c>
+      <c r="I9" s="3">
+        <v>8600</v>
       </c>
       <c r="J9" s="3">
         <v>8400</v>
@@ -981,11 +981,11 @@
       <c r="G10" s="3">
         <v>2100</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>24</v>
+      <c r="H10" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I10" s="3">
+        <v>2100</v>
       </c>
       <c r="J10" s="3">
         <v>2400</v>
@@ -1103,11 +1103,11 @@
       <c r="G12" s="3">
         <v>0</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>24</v>
+      <c r="H12" s="3">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0</v>
       </c>
       <c r="J12" s="3">
         <v>0</v>
@@ -1270,10 +1270,10 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>12700</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>12700</v>
       </c>
       <c r="F14" s="3">
         <v>-2900</v>
@@ -1281,11 +1281,11 @@
       <c r="G14" s="3">
         <v>-2900</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>24</v>
+      <c r="H14" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I14" s="3">
+        <v>1100</v>
       </c>
       <c r="J14" s="3">
         <v>-500</v>
@@ -1359,10 +1359,10 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>8700</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
-        <v>8700</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3">
         <v>0</v>
@@ -1371,10 +1371,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
@@ -1489,11 +1489,11 @@
       <c r="G17" s="3">
         <v>8600</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>24</v>
+      <c r="H17" s="3">
+        <v>9900</v>
+      </c>
+      <c r="I17" s="3">
+        <v>9900</v>
       </c>
       <c r="J17" s="3">
         <v>9600</v>
@@ -1578,11 +1578,11 @@
       <c r="G18" s="3">
         <v>1600</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>24</v>
+      <c r="H18" s="3">
+        <v>800</v>
+      </c>
+      <c r="I18" s="3">
+        <v>800</v>
       </c>
       <c r="J18" s="3">
         <v>1200</v>
@@ -1689,10 +1689,10 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>14400</v>
+        <v>1900</v>
       </c>
       <c r="E20" s="3">
-        <v>14400</v>
+        <v>1900</v>
       </c>
       <c r="F20" s="3">
         <v>-900</v>
@@ -1700,11 +1700,11 @@
       <c r="G20" s="3">
         <v>-900</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>24</v>
+      <c r="H20" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I20" s="3">
+        <v>1500</v>
       </c>
       <c r="J20" s="3">
         <v>400</v>
@@ -1778,10 +1778,10 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-13500</v>
+        <v>-9600</v>
       </c>
       <c r="E21" s="3">
-        <v>-13500</v>
+        <v>-9600</v>
       </c>
       <c r="F21" s="3">
         <v>2500</v>
@@ -1790,10 +1790,10 @@
         <v>2500</v>
       </c>
       <c r="H21" s="3">
-        <v>700</v>
+        <v>-600</v>
       </c>
       <c r="I21" s="3">
-        <v>700</v>
+        <v>-600</v>
       </c>
       <c r="J21" s="3">
         <v>800</v>
@@ -1878,11 +1878,11 @@
       <c r="G22" s="3">
         <v>0</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>24</v>
+      <c r="H22" s="3">
+        <v>100</v>
+      </c>
+      <c r="I22" s="3">
+        <v>100</v>
       </c>
       <c r="J22" s="3">
         <v>100</v>
@@ -1967,11 +1967,11 @@
       <c r="G23" s="3">
         <v>5500</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>24</v>
+      <c r="H23" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-1300</v>
       </c>
       <c r="J23" s="3">
         <v>1600</v>
@@ -2056,11 +2056,11 @@
       <c r="G24" s="3">
         <v>700</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>24</v>
+      <c r="H24" s="3">
+        <v>800</v>
+      </c>
+      <c r="I24" s="3">
+        <v>800</v>
       </c>
       <c r="J24" s="3">
         <v>700</v>
@@ -2234,11 +2234,11 @@
       <c r="G26" s="3">
         <v>4800</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>24</v>
+      <c r="H26" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-2100</v>
       </c>
       <c r="J26" s="3">
         <v>900</v>
@@ -2323,11 +2323,11 @@
       <c r="G27" s="3">
         <v>4800</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>24</v>
+      <c r="H27" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-2300</v>
       </c>
       <c r="J27" s="3">
         <v>700</v>
@@ -2502,10 +2502,10 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="I29" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="J29" s="3">
         <v>-300</v>
@@ -2757,10 +2757,10 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-14400</v>
+        <v>-1900</v>
       </c>
       <c r="E32" s="3">
-        <v>-14400</v>
+        <v>-1900</v>
       </c>
       <c r="F32" s="3">
         <v>900</v>
@@ -2768,11 +2768,11 @@
       <c r="G32" s="3">
         <v>900</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>24</v>
+      <c r="H32" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-1500</v>
       </c>
       <c r="J32" s="3">
         <v>-400</v>
@@ -2857,11 +2857,11 @@
       <c r="G33" s="3">
         <v>4800</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>24</v>
+      <c r="H33" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-2300</v>
       </c>
       <c r="J33" s="3">
         <v>700</v>
@@ -3035,11 +3035,11 @@
       <c r="G35" s="3">
         <v>4800</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>24</v>
+      <c r="H35" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-2300</v>
       </c>
       <c r="J35" s="3">
         <v>700</v>
@@ -3451,10 +3451,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>37800</v>
+        <v>40200</v>
       </c>
       <c r="E43" s="3">
-        <v>37800</v>
+        <v>40200</v>
       </c>
       <c r="F43" s="3">
         <v>40700</v>
@@ -3463,10 +3463,10 @@
         <v>40700</v>
       </c>
       <c r="H43" s="3">
-        <v>75700</v>
+        <v>77300</v>
       </c>
       <c r="I43" s="3">
-        <v>75700</v>
+        <v>77300</v>
       </c>
       <c r="J43" s="3">
         <v>82100</v>
@@ -3641,10 +3641,10 @@
         <v>700</v>
       </c>
       <c r="H45" s="3">
-        <v>5200</v>
+        <v>4700</v>
       </c>
       <c r="I45" s="3">
-        <v>5200</v>
+        <v>4700</v>
       </c>
       <c r="J45" s="3">
         <v>100</v>
@@ -4763,10 +4763,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4600</v>
+        <v>6100</v>
       </c>
       <c r="E59" s="3">
-        <v>4600</v>
+        <v>6100</v>
       </c>
       <c r="F59" s="3">
         <v>23700</v>
@@ -4775,10 +4775,10 @@
         <v>23700</v>
       </c>
       <c r="H59" s="3">
-        <v>6500</v>
+        <v>7600</v>
       </c>
       <c r="I59" s="3">
-        <v>6500</v>
+        <v>7600</v>
       </c>
       <c r="J59" s="3">
         <v>1900</v>
@@ -6503,11 +6503,11 @@
       <c r="G81" s="3">
         <v>4800</v>
       </c>
-      <c r="H81" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>24</v>
+      <c r="H81" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-2300</v>
       </c>
       <c r="J81" s="3">
         <v>700</v>
@@ -6613,11 +6613,11 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>24</v>
+      <c r="D83" s="3">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3">
+        <v>0</v>
       </c>
       <c r="F83" s="3">
         <v>0</v>
@@ -7159,11 +7159,11 @@
       <c r="G89" s="3">
         <v>-1700</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>24</v>
+      <c r="H89" s="3">
+        <v>500</v>
+      </c>
+      <c r="I89" s="3">
+        <v>500</v>
       </c>
       <c r="J89" s="3">
         <v>2200</v>
@@ -7281,11 +7281,11 @@
       <c r="G91" s="3">
         <v>0</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>24</v>
+      <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
@@ -7548,11 +7548,11 @@
       <c r="G94" s="3">
         <v>-300</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>24</v>
+      <c r="H94" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-1200</v>
       </c>
       <c r="J94" s="3">
         <v>-500</v>
@@ -8026,11 +8026,11 @@
       <c r="G100" s="3">
         <v>300</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>24</v>
+      <c r="H100" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I100" s="3">
+        <v>1000</v>
       </c>
       <c r="J100" s="3">
         <v>700</v>
@@ -8103,11 +8103,11 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>24</v>
+      <c r="D101" s="3">
+        <v>200</v>
+      </c>
+      <c r="E101" s="3">
+        <v>200</v>
       </c>
       <c r="F101" s="3">
         <v>0</v>
@@ -8205,10 +8205,10 @@
         <v>-1400</v>
       </c>
       <c r="H102" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="I102" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="J102" s="3">
         <v>2600</v>
